--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2020_T4_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2020_T4_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>75</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.61e+05</t>
-  </si>
-  <si>
-    <t>(70165.879)</t>
-  </si>
-  <si>
-    <t>497.409</t>
-  </si>
-  <si>
-    <t>(34.936)</t>
-  </si>
-  <si>
-    <t>3.609</t>
-  </si>
-  <si>
-    <t>(0.047)</t>
-  </si>
-  <si>
-    <t>10.197</t>
-  </si>
-  <si>
-    <t>(1.821)</t>
-  </si>
-  <si>
-    <t>88.319</t>
-  </si>
-  <si>
-    <t>(0.480)</t>
-  </si>
-  <si>
-    <t>1.04e+06</t>
-  </si>
-  <si>
-    <t>(55789.216)</t>
-  </si>
-  <si>
-    <t>2.498</t>
-  </si>
-  <si>
-    <t>(0.131)</t>
-  </si>
-  <si>
-    <t>3.316</t>
-  </si>
-  <si>
-    <t>(0.452)</t>
-  </si>
-  <si>
-    <t>33.658</t>
-  </si>
-  <si>
-    <t>(3.604)</t>
-  </si>
-  <si>
-    <t>0.947</t>
-  </si>
-  <si>
-    <t>(0.026)</t>
-  </si>
-  <si>
-    <t>40</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>7.15e+05</t>
-  </si>
-  <si>
-    <t>(1.34e+05)</t>
-  </si>
-  <si>
-    <t>483.564</t>
-  </si>
-  <si>
-    <t>(52.955)</t>
-  </si>
-  <si>
-    <t>3.346</t>
-  </si>
-  <si>
-    <t>(0.057)</t>
-  </si>
-  <si>
-    <t>27.100</t>
-  </si>
-  <si>
-    <t>(4.016)</t>
-  </si>
-  <si>
-    <t>91.265</t>
-  </si>
-  <si>
-    <t>(0.461)</t>
-  </si>
-  <si>
-    <t>1.34e+06</t>
-  </si>
-  <si>
-    <t>(70734.241)</t>
-  </si>
-  <si>
-    <t>3.317</t>
-  </si>
-  <si>
-    <t>(0.144)</t>
-  </si>
-  <si>
-    <t>6.075</t>
-  </si>
-  <si>
-    <t>(0.615)</t>
-  </si>
-  <si>
-    <t>43.350</t>
-  </si>
-  <si>
-    <t>(3.450)</t>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.54e+05</t>
-  </si>
-  <si>
-    <t>-13.845</t>
-  </si>
-  <si>
-    <t>-0.263***</t>
-  </si>
-  <si>
-    <t>16.903***</t>
-  </si>
-  <si>
-    <t>2.946***</t>
-  </si>
-  <si>
-    <t>3.01e+05***</t>
-  </si>
-  <si>
-    <t>0.819***</t>
-  </si>
-  <si>
-    <t>2.759***</t>
-  </si>
-  <si>
-    <t>9.692*</t>
-  </si>
-  <si>
-    <t>0.053</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2020_T4_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2020_T4_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>76</t>
+  </si>
+  <si>
+    <t>75</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
+    <t>5.61e+05</t>
+  </si>
+  <si>
+    <t>(70165.879)</t>
+  </si>
+  <si>
+    <t>497.409</t>
+  </si>
+  <si>
+    <t>(34.936)</t>
+  </si>
+  <si>
+    <t>3.609</t>
+  </si>
+  <si>
+    <t>(0.047)</t>
+  </si>
+  <si>
+    <t>10.197</t>
+  </si>
+  <si>
+    <t>(1.821)</t>
+  </si>
+  <si>
+    <t>88.319</t>
+  </si>
+  <si>
+    <t>(0.480)</t>
+  </si>
+  <si>
+    <t>1.04e+06</t>
+  </si>
+  <si>
+    <t>(55789.216)</t>
+  </si>
+  <si>
+    <t>2.498</t>
+  </si>
+  <si>
+    <t>(0.131)</t>
+  </si>
+  <si>
+    <t>3.316</t>
+  </si>
+  <si>
+    <t>(0.452)</t>
+  </si>
+  <si>
+    <t>33.658</t>
+  </si>
+  <si>
+    <t>(3.604)</t>
+  </si>
+  <si>
+    <t>0.947</t>
+  </si>
+  <si>
+    <t>(0.026)</t>
+  </si>
+  <si>
+    <t>40</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>7.15e+05</t>
+  </si>
+  <si>
+    <t>(1.34e+05)</t>
+  </si>
+  <si>
+    <t>483.564</t>
+  </si>
+  <si>
+    <t>(52.955)</t>
+  </si>
+  <si>
+    <t>3.346</t>
+  </si>
+  <si>
+    <t>(0.057)</t>
+  </si>
+  <si>
+    <t>27.100</t>
+  </si>
+  <si>
+    <t>(4.016)</t>
+  </si>
+  <si>
+    <t>91.265</t>
+  </si>
+  <si>
+    <t>(0.461)</t>
+  </si>
+  <si>
+    <t>1.34e+06</t>
+  </si>
+  <si>
+    <t>(70734.241)</t>
+  </si>
+  <si>
+    <t>3.317</t>
+  </si>
+  <si>
+    <t>(0.144)</t>
+  </si>
+  <si>
+    <t>6.075</t>
+  </si>
+  <si>
+    <t>(0.615)</t>
+  </si>
+  <si>
+    <t>43.350</t>
+  </si>
+  <si>
+    <t>(3.450)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>1.54e+05</t>
+  </si>
+  <si>
+    <t>-13.845</t>
+  </si>
+  <si>
+    <t>-0.263***</t>
+  </si>
+  <si>
+    <t>16.903***</t>
+  </si>
+  <si>
+    <t>2.946***</t>
+  </si>
+  <si>
+    <t>3.01e+05***</t>
+  </si>
+  <si>
+    <t>0.819***</t>
+  </si>
+  <si>
+    <t>2.759***</t>
+  </si>
+  <si>
+    <t>9.692*</t>
+  </si>
+  <si>
+    <t>0.053</t>
   </si>
 </sst>
 </file>
